--- a/artfynd/A 8074-2020 artfynd.xlsx
+++ b/artfynd/A 8074-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8074-2020 artfynd.xlsx
+++ b/artfynd/A 8074-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,6 +1429,130 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118865435</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Gålleryd, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>431954</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6422341</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nykyrka</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Bergström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Bergström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8074-2020 artfynd.xlsx
+++ b/artfynd/A 8074-2020 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>121080251</v>
       </c>
       <c r="B9" t="n">
-        <v>57499</v>
+        <v>57502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 8074-2020 artfynd.xlsx
+++ b/artfynd/A 8074-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116486002</v>
+        <v>116486001</v>
       </c>
       <c r="B5" t="n">
-        <v>57746</v>
+        <v>57603</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,21 +1071,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1094,14 +1094,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1146,7 +1142,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1152,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116486001</v>
+        <v>116702552</v>
       </c>
       <c r="B6" t="n">
-        <v>57603</v>
+        <v>56624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,20 +1191,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103008</v>
+        <v>100065</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1225,7 +1221,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1265,22 +1261,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,10 +1303,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116702552</v>
+        <v>118865435</v>
       </c>
       <c r="B7" t="n">
-        <v>56624</v>
+        <v>57308</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1319,20 +1315,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1349,23 +1345,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Änglagård, Mullsjö, Vg</t>
+          <t>Lilla Gålleryd, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431884</v>
+        <v>431954</v>
       </c>
       <c r="R7" t="n">
-        <v>6422375</v>
+        <v>6422341</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,22 +1385,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,254 +1424,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>118865435</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Lilla Gålleryd, Vg</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>431954</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6422341</v>
-      </c>
-      <c r="S8" t="n">
-        <v>100</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Mullsjö</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Nykyrka</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Michael Bergström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Michael Bergström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>121080251</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57502</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>103020</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Entita</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Poecile palustris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Änglagård, Mullsjö, Vg</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>431884</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6422375</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Mullsjö</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Nykyrka</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-11-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Michael Bergström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Michael Bergström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
